--- a/stories/arbres/TREE-COL-005.xlsx
+++ b/stories/arbres/TREE-COL-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est près de la fenêtre avec papa. Un oiseau passe. Papa dit : aujourd'hui on salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots.</t>
+          <t>Jules est près de la fenêtre avec papa. Un oiseau passe. Aujourd'hui on salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est près de la fenêtre avec papa. Un oiseau passe.
+papa|Aujourd'hui on salue. On dit bonjour. On dit s'il te plaît. On dit merci.
+narrateur|Jules répète les trois mots.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la cuisine. Ça sent le pain chaud. papa est tout près. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Jules a retenu. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le voisin. L'eau coule. papa montre lentement. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. Un vélo passe. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la maîtresse. Le vent est doux. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la boulangère. Il y a des miettes. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le jardin. Une feuille tombe. papa est tout près. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6479,6 +6653,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6503,7 +6682,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Jules respire. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit : je suis là.</t>
+          <t>Jules respire. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6645,6 +6824,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Jules respire. Jules dit bonjour. Il dit s'il te plaît. Il dit merci.
+papa|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7016,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7183,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le voisin. Un vélo passe. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7374,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7541,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7708,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7875,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8042,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8209,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8376,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8543,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la maîtresse. Un chat miaule. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8734,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8901,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9068,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9235,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9402,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9569,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9736,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9903,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la boulangère. La lumière est claire. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10094,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10261,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10428,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10595,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10762,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10929,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11096,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11263,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la chambre. La couverture est douce. papa est tout près. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Jules donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le voisin. Les chaussures font toc. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la maîtresse. On entend un oiseau. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la boulangère. Le sol est un peu froid. papa montre lentement. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le pain. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint une pomme. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint un livre. Ça sent le pain chaud. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-005.xlsx
+++ b/stories/arbres/TREE-COL-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Jules répète les trois mots.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Jules va vers la cuisine. Ça sent le pain chaud. papa est tout près. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Jules salue. Quels mots dit-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Jules a retenu. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Jules a choisi le voisin. L'eau coule. papa montre lentement. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Jules rejoint le pain. Un vélo passe. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Jules rejoint une pomme. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Jules rejoint un livre. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Jules a choisi la maîtresse. Le vent est doux. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5142,7 @@
           <t>narrateur|Jules a choisi la boulangère. Il y a des miettes. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5334,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5502,7 @@
           <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5670,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5838,7 @@
           <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6174,7 @@
           <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
           <t>narrateur|Jules va vers le jardin. Une feuille tombe. papa est tout près. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Jules salue. Quels mots dit-il ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6830,6 +6867,7 @@
 papa|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7021,6 +7059,7 @@
           <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7188,6 +7227,7 @@
           <t>narrateur|Jules a choisi le voisin. Un vélo passe. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7379,6 +7419,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7546,6 +7587,7 @@
           <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7713,6 +7755,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7880,6 +7923,7 @@
           <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8047,6 +8091,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8214,6 +8259,7 @@
           <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8381,6 +8427,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8548,6 +8595,7 @@
           <t>narrateur|Jules a choisi la maîtresse. Un chat miaule. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8739,6 +8787,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8906,6 +8955,7 @@
           <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9073,6 +9123,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9240,6 +9291,7 @@
           <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9407,6 +9459,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9574,6 +9627,7 @@
           <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9741,6 +9795,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9908,6 +9963,7 @@
           <t>narrateur|Jules a choisi la boulangère. La lumière est claire. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10099,6 +10155,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10266,6 +10323,7 @@
           <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10433,6 +10491,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10600,6 +10659,7 @@
           <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10767,6 +10827,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10934,6 +10995,7 @@
           <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11101,6 +11163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
           <t>narrateur|Jules va vers la chambre. La couverture est douce. papa est tout près. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Jules salue. Quels mots dit-il ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|C'est juste. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Jules donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Jules a choisi le voisin. Les chaussures font toc. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Jules a choisi la maîtresse. On entend un oiseau. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Jules a choisi la boulangère. Le sol est un peu froid. papa montre lentement. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Jules rejoint le pain. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Jules rejoint une pomme. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Jules rejoint un livre. Ça sent le pain chaud. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-005.xlsx
+++ b/stories/arbres/TREE-COL-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules dit bonjour, s'il te plaît, merci</t>
+          <t>La gouttière et les trois mots d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie a laissé des rivières sur la vitre. Aniss dit bonjour, s'il te plaît, merci, de la cuisine au jardin, jusqu'au pain, à la pomme ou au livre.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est près de la fenêtre avec papa. Un oiseau passe. Aujourd'hui on salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots.</t>
+          <t>La gouttière fait un petit tic, tic, tic. La pluie a laissé des rivières sur la vitre. La vitre est tiède du côté de la maison. De l'autre côté, l'air sent l'herbe mouillée. Les chaussures de papa sèchent près de la porte. Une chaussette rouge pend encore. Dans la cuisine, la soupe fume tout doux. Ça sent la carotte et le thym. Un oiseau secoue ses plumes sur la haie. Il est tout petit, tout gris. Tu entends la gouttière, Aniss ? Oui, maman. Tic, tic. Les chaussures sont encore un peu mouillées. On les laisse là. En ce moment, Aniss trace une rivière sur la vitre. Son doigt fait un chemin clair. Je vois l'oiseau. On dit bonjour, Aniss. Bonjour. Si tu demandes, tu dis s'il te plaît. S'il te plaît. Et après, merci. Merci. Bravo. Les trois mots. L'oiseau s'envole. La haie brille. Tu es prêt à bouger ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,9 +1337,36 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est près de la fenêtre avec papa. Un oiseau passe.
-papa|Aujourd'hui on salue. On dit bonjour. On dit s'il te plaît. On dit merci.
-narrateur|Jules répète les trois mots.</t>
+          <t>narrateur|La gouttière fait un petit tic, tic, tic.
+narrateur|La pluie a laissé des rivières sur la vitre.
+narrateur|La vitre est tiède du côté de la maison.
+narrateur|De l'autre côté, l'air sent l'herbe mouillée.
+narrateur|Les chaussures de papa sèchent près de la porte.
+narrateur|Une chaussette rouge pend encore.
+narrateur|Dans la cuisine, la soupe fume tout doux.
+narrateur|Ça sent la carotte et le thym.
+narrateur|Un oiseau secoue ses plumes sur la haie.
+narrateur|Il est tout petit, tout gris.
+maman|Tu entends la gouttière, Aniss ?
+enfant-m|Oui, maman.
+enfant-m|Tic, tic.
+papa|Les chaussures sont encore un peu mouillées.
+papa|On les laisse là.
+narrateur|En ce moment, Aniss trace une rivière sur la vitre.
+narrateur|Son doigt fait un chemin clair.
+enfant-m|Je vois l'oiseau.
+maman|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Si tu demandes, tu dis s'il te plaît.
+enfant-m|S'il te plaît.
+maman|Et après, merci.
+enfant-m|Merci.
+papa|Bravo.
+papa|Les trois mots.
+narrateur|L'oiseau s'envole.
+narrateur|La haie brille.
+maman|Tu es prêt à bouger ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1355,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>La maison a trois endroits, tout près. La cuisine, le jardin, ou la chambre ? Tu choisis. Ensuite on dit les mots.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1519,7 +1558,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|La maison a trois endroits, tout près.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|Tu choisis.
+maman|Ensuite on dit les mots.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1547,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la cuisine. Ça sent le pain chaud. papa est tout près. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>La cuisine sent la soupe et le pain. La table de bois est un peu tiède. La vapeur dessine un nuage sur la vitre. Une miette dorée attend près de l'assiette. Tu dis bonjour, Aniss ? Bonjour, maman. Bravo. Tu veux un bout de croûte ? Oui. S'il te plaît. Maman casse un bout de croûte. Croc. Le pain est encore chaud. Merci. Tu as dit les trois mots. Tu as fait du bon travail. La soupe fume encore. Tu la sens ? Oui. Ça sent le thym. Une goutte glisse sur la vitre, tout lentement.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1687,7 +1729,27 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers la cuisine. Ça sent le pain chaud. papa est tout près. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>narrateur|La cuisine sent la soupe et le pain.
+narrateur|La table de bois est un peu tiède.
+narrateur|La vapeur dessine un nuage sur la vitre.
+narrateur|Une miette dorée attend près de l'assiette.
+maman|Tu dis bonjour, Aniss ?
+enfant-m|Bonjour, maman.
+papa|Bravo.
+papa|Tu veux un bout de croûte ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|Maman casse un bout de croûte.
+narrateur|Croc.
+narrateur|Le pain est encore chaud.
+enfant-m|Merci.
+maman|Tu as dit les trois mots.
+maman|Tu as fait du bon travail.
+papa|La soupe fume encore.
+papa|Tu la sens ?
+enfant-m|Oui.
+enfant-m|Ça sent le thym.
+narrateur|Une goutte glisse sur la vitre, tout lentement.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1715,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules salue. Quels mots dit-il ?</t>
+          <t>Aniss est dans la cuisine. Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1933,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
+          <t>narrateur|Aniss est dans la cuisine.
+maman|Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Jules a retenu. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. On continue avec papa.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bonjour. S'il te plaît. Merci. Oui. Bravo, Aniss. La miette dorée n'est plus sur la table. On continue, tout doux. Oui, papa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2106,17 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Jules a retenu. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. On continue avec papa.</t>
+          <t>papa|Bonjour.
+maman|S'il te plaît.
+papa|Merci.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Oui.
+maman|Bravo, Aniss.
+narrateur|La miette dorée n'est plus sur la table.
+papa|On continue, tout doux.
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2144,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>L'odeur du thym suit encore Aniss. On peut aller vers quelqu'un, maintenant. Le voisin, la maîtresse, ou la boulangère ? Tu choisis.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2235,7 +2308,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+papa|On peut aller vers quelqu'un, maintenant.
+maman|Le voisin, la maîtresse, ou la boulangère ?
+papa|Tu choisis.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2263,7 +2339,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le voisin. L'eau coule. papa montre lentement. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>L'odeur du thym suit encore Aniss. Le portail de bois est encore mouillé. Une goutte tombe. Plic. Le voisin range un arrosoir bleu. On dit bonjour, Aniss. Bonjour. Bravo. Si tu demandes, tu dis s'il te plaît. S'il te plaît. L'arrosoir brille. L'eau sent la terre. Et après ? Merci. Tu as dit les trois mots. Tu as fait du bon travail. Le portail est froid. On reste près de toi. Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2403,7 +2479,25 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le voisin. L'eau coule. papa montre lentement. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le portail de bois est encore mouillé.
+narrateur|Une goutte tombe.
+narrateur|Plic.
+narrateur|Le voisin range un arrosoir bleu.
+papa|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Si tu demandes, tu dis s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|L'arrosoir brille.
+narrateur|L'eau sent la terre.
+papa|Et après ?
+enfant-m|Merci.
+maman|Tu as dit les trois mots.
+papa|Tu as fait du bon travail.
+enfant-m|Le portail est froid.
+maman|On reste près de toi.
+narrateur|Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2431,7 +2525,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le portail de bois brille encore. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2595,7 +2689,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le portail de bois brille encore.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2623,7 +2720,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. Un vélo passe. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>L'odeur du thym suit encore Aniss. Le portail de bois brille encore. Une miette de pain reste sur le bois, près de la haie. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2763,7 +2860,27 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. Un vélo passe. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le portail de bois brille encore.
+narrateur|Une miette de pain reste sur le bois, près de la haie.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2791,7 +2908,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué le voisin. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2931,7 +3048,18 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2959,7 +3087,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>L'odeur du thym suit encore Aniss. Le portail de bois brille encore. La pomme brille, encore un peu mouillée près du portail. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3099,7 +3227,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le portail de bois brille encore.
+narrateur|La pomme brille, encore un peu mouillée près du portail.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3127,7 +3276,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué le voisin. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3267,7 +3416,18 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3295,7 +3455,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>L'odeur du thym suit encore Aniss. Le portail de bois brille encore. Le livre a une goutte ronde sur la couverture. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3435,7 +3595,30 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis le voisin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le portail de bois brille encore.
+narrateur|Le livre a une goutte ronde sur la couverture.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3463,7 +3646,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué le voisin. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3603,7 +3786,18 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3631,7 +3825,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la maîtresse. Le vent est doux. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>L'odeur du thym suit encore Aniss. La porte de l'école sent le bois mouillé. Un grelot de vélo sonne, loin, une fois. La maîtresse tient un livre fermé. Bonjour, Aniss. Bonjour. Bravo. Tu demandes avec s'il te plaît. S'il te plaît. La maîtresse ouvre le livre. Les pages sentent le papier. Merci. Merci, Aniss. Tu as dit les trois mots. Tu as fait du bon travail. Le livre a une image d'oiseau. Oui. On reste ensemble. Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3771,7 +3965,25 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la maîtresse. Le vent est doux. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|La porte de l'école sent le bois mouillé.
+narrateur|Un grelot de vélo sonne, loin, une fois.
+narrateur|La maîtresse tient un livre fermé.
+maitresse|Bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+maman|Tu demandes avec s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|La maîtresse ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maitresse|Merci, Aniss.
+papa|Tu as dit les trois mots.
+maman|Tu as fait du bon travail.
+enfant-m|Le livre a une image d'oiseau.
+papa|Oui.
+papa|On reste ensemble.
+narrateur|Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3799,7 +4011,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le livre de la maîtresse reste sous son bras. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3963,7 +4175,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le livre de la maîtresse reste sous son bras.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3991,7 +4206,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>L'odeur du thym suit encore Aniss. Le livre de la maîtresse reste sous son bras. Le pain sent le four, jusque dans l'entrée de l'école. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4131,7 +4346,27 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Le pain sent le four, jusque dans l'entrée de l'école.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4159,7 +4394,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la maîtresse. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4299,7 +4534,18 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4327,7 +4573,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>L'odeur du thym suit encore Aniss. Le livre de la maîtresse reste sous son bras. La pomme fait un petit bruit, sur la table de la classe. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4467,7 +4713,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|La pomme fait un petit bruit, sur la table de la classe.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4495,7 +4762,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la maîtresse. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4635,7 +4902,18 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4663,7 +4941,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>L'odeur du thym suit encore Aniss. Le livre de la maîtresse reste sous son bras. Le livre s'ouvre. L'image sent encore le thym. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4803,7 +5081,31 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la maîtresse.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Le livre s'ouvre.
+narrateur|L'image sent encore le thym.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4831,7 +5133,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la maîtresse. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4971,7 +5273,18 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4999,7 +5312,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la boulangère. Il y a des miettes. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>L'odeur du thym suit encore Aniss. La porte de la boulangerie s'ouvre. Une petite cloche fait ding. L'air chaud sent le beurre et le four. On dit bonjour, Aniss. Bonjour. Bravo. Tu demandes, maintenant. S'il te plaît. La boulangère a de la farine sur le tablier. Le bois du comptoir est lisse, un peu blanc. Merci. Tu as dit merci. Tu as fait du bon travail. Ça sent le pain. Oui. On reste près du comptoir. Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5139,7 +5452,24 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la boulangère. Il y a des miettes. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|La porte de la boulangerie s'ouvre.
+narrateur|Une petite cloche fait ding.
+narrateur|L'air chaud sent le beurre et le four.
+maman|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+papa|Tu demandes, maintenant.
+enfant-m|S'il te plaît.
+narrateur|La boulangère a de la farine sur le tablier.
+narrateur|Le bois du comptoir est lisse, un peu blanc.
+enfant-m|Merci.
+maman|Tu as dit merci.
+maman|Tu as fait du bon travail.
+enfant-m|Ça sent le pain.
+papa|Oui.
+papa|On reste près du comptoir.
+narrateur|Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5167,7 +5497,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>La petite cloche a encore fait ding. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5331,7 +5661,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|La petite cloche a encore fait ding.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5359,7 +5692,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>L'odeur du thym suit encore Aniss. La petite cloche a encore fait ding. Le sachet de pain est tiède, sous la cloche de la boutique. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5499,7 +5832,27 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le sachet de pain est tiède, sous la cloche de la boutique.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5527,7 +5880,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la boulangère. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5667,7 +6020,18 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5695,7 +6059,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>L'odeur du thym suit encore Aniss. La petite cloche a encore fait ding. La pomme roule un peu, sur le comptoir fariné. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5835,7 +6199,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|La petite cloche a encore fait ding.
+narrateur|La pomme roule un peu, sur le comptoir fariné.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5863,7 +6248,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la boulangère. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6003,7 +6388,18 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6031,7 +6427,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. On entend un oiseau. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>L'odeur du thym suit encore Aniss. La petite cloche a encore fait ding. Le livre se pose près des croûtes dorées. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6171,7 +6567,30 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la cuisine, puis la boulangère.</t>
+          <t>narrateur|L'odeur du thym suit encore Aniss.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le livre se pose près des croûtes dorées.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6199,7 +6618,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la cuisine. Il a salué la boulangère. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6339,7 +6758,18 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la cuisine.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6367,7 +6797,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le jardin. Une feuille tombe. papa est tout près. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>Le jardin brille, encore mouillé. Une flaque ronde tient un morceau de ciel. Une feuille jaune colle au bois du banc. L'herbe sent la pluie et la terre. On dit bonjour au jardin, Aniss. Bonjour. Tu veux la feuille jaune ? S'il te plaît. Papa tend la feuille. Elle est froide, un peu lisse. Merci, papa. Bravo. Les trois mots. Tu as les pieds au sec ? Oui. Les bottes sont chaudes. Un oiseau secoue ses plumes sur la haie. Plic. Une goutte tombe dans la flaque. Tu as fait du bon travail. La feuille sent l'herbe.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6507,7 +6937,27 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le jardin. Une feuille tombe. papa est tout près. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>narrateur|Le jardin brille, encore mouillé.
+narrateur|Une flaque ronde tient un morceau de ciel.
+narrateur|Une feuille jaune colle au bois du banc.
+narrateur|L'herbe sent la pluie et la terre.
+papa|On dit bonjour au jardin, Aniss.
+enfant-m|Bonjour.
+maman|Tu veux la feuille jaune ?
+enfant-m|S'il te plaît.
+narrateur|Papa tend la feuille.
+narrateur|Elle est froide, un peu lisse.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu as les pieds au sec ?
+enfant-m|Oui.
+enfant-m|Les bottes sont chaudes.
+narrateur|Un oiseau secoue ses plumes sur la haie.
+narrateur|Plic.
+narrateur|Une goutte tombe dans la flaque.
+maman|Tu as fait du bon travail.
+enfant-m|La feuille sent l'herbe.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6535,7 +6985,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Jules salue. Quels mots dit-il ?</t>
+          <t>Aniss est dans le jardin. Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6691,7 +7141,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
+          <t>narrateur|Aniss est dans le jardin.
+papa|Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6719,7 +7170,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Jules respire. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Je suis là.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bonjour. S'il te plaît. Merci. Oui. Bravo, Aniss. La feuille jaune tremble un peu, entre ses doigts. On continue, tout près. Oui, maman.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6863,8 +7314,17 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Jules respire. Jules dit bonjour. Il dit s'il te plaît. Il dit merci.
-papa|Je suis là.</t>
+          <t>maman|Bonjour.
+papa|S'il te plaît.
+maman|Merci.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+papa|Oui.
+papa|Bravo, Aniss.
+narrateur|La feuille jaune tremble un peu, entre ses doigts.
+maman|On continue, tout près.
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6892,7 +7352,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. On peut aller vers quelqu'un, maintenant. Le voisin, la maîtresse, ou la boulangère ? Tu choisis.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7056,7 +7516,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+papa|On peut aller vers quelqu'un, maintenant.
+maman|Le voisin, la maîtresse, ou la boulangère ?
+papa|Tu choisis.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7084,7 +7547,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le voisin. Un vélo passe. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le portail de bois est encore mouillé. Une goutte tombe. Plic. Le voisin range un arrosoir bleu. On dit bonjour, Aniss. Bonjour. Bravo. Si tu demandes, tu dis s'il te plaît. S'il te plaît. L'arrosoir brille. L'eau sent la terre. Et après ? Merci. Tu as dit les trois mots. Tu as fait du bon travail. Le portail est froid. On reste près de toi. Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7224,7 +7687,25 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le voisin. Un vélo passe. papa montre lentement. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le portail de bois est encore mouillé.
+narrateur|Une goutte tombe.
+narrateur|Plic.
+narrateur|Le voisin range un arrosoir bleu.
+papa|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Si tu demandes, tu dis s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|L'arrosoir brille.
+narrateur|L'eau sent la terre.
+papa|Et après ?
+enfant-m|Merci.
+maman|Tu as dit les trois mots.
+papa|Tu as fait du bon travail.
+enfant-m|Le portail est froid.
+maman|On reste près de toi.
+narrateur|Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7252,7 +7733,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le portail de bois brille encore. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7416,7 +7897,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le portail de bois brille encore.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7444,7 +7928,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. Un chat miaule. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le portail de bois brille encore. Une feuille mouillée colle au sachet du pain. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7584,7 +8068,27 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. Un chat miaule. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le portail de bois brille encore.
+narrateur|Une feuille mouillée colle au sachet du pain.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7612,7 +8116,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué le voisin. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7752,7 +8256,18 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7780,7 +8295,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le portail de bois brille encore. La pomme a senti l'herbe, tout près de la haie. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7920,7 +8435,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le portail de bois brille encore.
+narrateur|La pomme a senti l'herbe, tout près de la haie.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7948,7 +8484,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué le voisin. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8088,7 +8624,18 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8116,7 +8663,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le portail de bois brille encore. Le livre a une petite tache d'eau, déjà sèche. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8256,7 +8803,30 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis le voisin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le portail de bois brille encore.
+narrateur|Le livre a une petite tache d'eau, déjà sèche.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8284,7 +8854,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué le voisin. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8424,7 +8994,18 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8452,7 +9033,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la maîtresse. Un chat miaule. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. La porte de l'école sent le bois mouillé. Un grelot de vélo sonne, loin, une fois. La maîtresse tient un livre fermé. Bonjour, Aniss. Bonjour. Bravo. Tu demandes avec s'il te plaît. S'il te plaît. La maîtresse ouvre le livre. Les pages sentent le papier. Merci. Merci, Aniss. Tu as dit les trois mots. Tu as fait du bon travail. Le livre a une image d'oiseau. Oui. On reste ensemble. Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8592,7 +9173,25 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la maîtresse. Un chat miaule. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|La porte de l'école sent le bois mouillé.
+narrateur|Un grelot de vélo sonne, loin, une fois.
+narrateur|La maîtresse tient un livre fermé.
+maitresse|Bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+maman|Tu demandes avec s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|La maîtresse ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maitresse|Merci, Aniss.
+papa|Tu as dit les trois mots.
+maman|Tu as fait du bon travail.
+enfant-m|Le livre a une image d'oiseau.
+papa|Oui.
+papa|On reste ensemble.
+narrateur|Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8620,7 +9219,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le livre de la maîtresse reste sous son bras. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8784,7 +9383,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le livre de la maîtresse reste sous son bras.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8812,7 +9414,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le livre de la maîtresse reste sous son bras. Des gouttes brillent encore sur le pain, dans la cour. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8952,7 +9554,27 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Des gouttes brillent encore sur le pain, dans la cour.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8980,7 +9602,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la maîtresse. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9120,7 +9742,18 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9148,7 +9781,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le livre de la maîtresse reste sous son bras. La pomme est froide, comme la flaque du jardin. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9288,7 +9921,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|La pomme est froide, comme la flaque du jardin.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9316,7 +9970,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la maîtresse. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9456,7 +10110,18 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9484,7 +10149,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. Le livre de la maîtresse reste sous son bras. Le livre sent l'herbe, sous le regard de la maîtresse. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9624,7 +10289,30 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la maîtresse.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Le livre sent l'herbe, sous le regard de la maîtresse.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9652,7 +10340,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la maîtresse. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9792,7 +10480,18 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9820,7 +10519,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la boulangère. La lumière est claire. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. La porte de la boulangerie s'ouvre. Une petite cloche fait ding. L'air chaud sent le beurre et le four. On dit bonjour, Aniss. Bonjour. Bravo. Tu demandes, maintenant. S'il te plaît. La boulangère a de la farine sur le tablier. Le bois du comptoir est lisse, un peu blanc. Merci. Tu as dit merci. Tu as fait du bon travail. Ça sent le pain. Oui. On reste près du comptoir. Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9960,7 +10659,24 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la boulangère. La lumière est claire. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|La porte de la boulangerie s'ouvre.
+narrateur|Une petite cloche fait ding.
+narrateur|L'air chaud sent le beurre et le four.
+maman|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+papa|Tu demandes, maintenant.
+enfant-m|S'il te plaît.
+narrateur|La boulangère a de la farine sur le tablier.
+narrateur|Le bois du comptoir est lisse, un peu blanc.
+enfant-m|Merci.
+maman|Tu as dit merci.
+maman|Tu as fait du bon travail.
+enfant-m|Ça sent le pain.
+papa|Oui.
+papa|On reste près du comptoir.
+narrateur|Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9988,7 +10704,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>La petite cloche a encore fait ding. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10152,7 +10868,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|La petite cloche a encore fait ding.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10180,7 +10899,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. La petite cloche a encore fait ding. Le pain chaud réchauffe les doigts encore froids du jardin. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10320,7 +11039,27 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le pain chaud réchauffe les doigts encore froids du jardin.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10348,7 +11087,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la boulangère. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10488,7 +11227,18 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10516,7 +11266,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. La petite cloche a encore fait ding. La pomme brille entre les miettes, à la boulangerie. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10656,7 +11406,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|La petite cloche a encore fait ding.
+narrateur|La pomme brille entre les miettes, à la boulangerie.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10684,7 +11455,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la boulangère. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10824,7 +11595,18 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10852,7 +11634,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. Le sol est un peu froid. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>Une feuille mouillée reste collée à sa chaussure. La petite cloche a encore fait ding. Le livre a une odeur d'herbe et de four, ensemble. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10992,7 +11774,30 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. le jardin, puis la boulangère.</t>
+          <t>narrateur|Une feuille mouillée reste collée à sa chaussure.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le livre a une odeur d'herbe et de four, ensemble.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11020,7 +11825,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans le jardin. Il a salué la boulangère. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11160,7 +11965,18 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans le jardin.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11188,7 +12004,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la chambre. La couverture est douce. papa est tout près. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>La chambre est calme, un peu sombre. Un rayon jaune pose une barre sur le tapis. Le tapis est doux, un peu rêche au bord. Le doudou attend contre l'oreiller. Bonjour, la chambre. Bonjour. Tu veux le doudou ? S'il te plaît. Maman tend le doudou. Il sent le lit. Merci, maman. Bravo, Aniss. Tu as dit s'il te plaît. Et merci. C'est bien. Le doudou a une oreille un peu pliée. Il est chaud. Tu as fini de le serrer ? Encore un peu. Le rayon avance, tout lent, sur le bois.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11328,7 +12144,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers la chambre. La couverture est douce. papa est tout près. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa sourit.</t>
+          <t>narrateur|La chambre est calme, un peu sombre.
+narrateur|Un rayon jaune pose une barre sur le tapis.
+narrateur|Le tapis est doux, un peu rêche au bord.
+narrateur|Le doudou attend contre l'oreiller.
+maman|Bonjour, la chambre.
+enfant-m|Bonjour.
+papa|Tu veux le doudou ?
+enfant-m|S'il te plaît.
+narrateur|Maman tend le doudou.
+narrateur|Il sent le lit.
+enfant-m|Merci, maman.
+papa|Bravo, Aniss.
+papa|Tu as dit s'il te plaît.
+maman|Et merci.
+maman|C'est bien.
+narrateur|Le doudou a une oreille un peu pliée.
+enfant-m|Il est chaud.
+maman|Tu as fini de le serrer ?
+enfant-m|Encore un peu.
+narrateur|Le rayon avance, tout lent, sur le bois.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11356,7 +12191,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Jules salue. Quels mots dit-il ?</t>
+          <t>Aniss est dans la chambre. Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11512,7 +12347,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Jules salue. Quels mots dit-il ?</t>
+          <t>narrateur|Aniss est dans la chambre.
+maman|Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11540,7 +12376,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>C'est juste. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Jules donne la main à papa.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bonjour. S'il te plaît. Merci. Oui. Bravo, Aniss. L'oreille du doudou se déplie un peu. On continue, avec nous. Oui, papa.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11684,7 +12520,17 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|C'est juste. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Jules donne la main à papa.</t>
+          <t>papa|Bonjour.
+maman|S'il te plaît.
+papa|Merci.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Oui.
+maman|Bravo, Aniss.
+narrateur|L'oreille du doudou se déplie un peu.
+papa|On continue, avec nous.
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11712,7 +12558,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>Le doudou reste sur le lit, tout calme. On peut aller vers quelqu'un, maintenant. Le voisin, la maîtresse, ou la boulangère ? Tu choisis.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11876,7 +12722,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le voisin, la maîtresse, ou la boulangère.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+papa|On peut aller vers quelqu'un, maintenant.
+maman|Le voisin, la maîtresse, ou la boulangère ?
+papa|Tu choisis.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11904,7 +12753,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le voisin. Les chaussures font toc. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le portail de bois est encore mouillé. Une goutte tombe. Plic. Le voisin range un arrosoir bleu. On dit bonjour, Aniss. Bonjour. Bravo. Si tu demandes, tu dis s'il te plaît. S'il te plaît. L'arrosoir brille. L'eau sent la terre. Et après ? Merci. Tu as dit les trois mots. Tu as fait du bon travail. Le portail est froid. On reste près de toi. Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12044,7 +12893,25 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le voisin. Les chaussures font toc. papa montre lentement. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le portail de bois est encore mouillé.
+narrateur|Une goutte tombe.
+narrateur|Plic.
+narrateur|Le voisin range un arrosoir bleu.
+papa|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Si tu demandes, tu dis s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|L'arrosoir brille.
+narrateur|L'eau sent la terre.
+papa|Et après ?
+enfant-m|Merci.
+maman|Tu as dit les trois mots.
+papa|Tu as fait du bon travail.
+enfant-m|Le portail est froid.
+maman|On reste près de toi.
+narrateur|Une abeille passe, tout bas, le long de la haie.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12072,7 +12939,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le portail de bois brille encore. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12236,7 +13103,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le portail de bois brille encore.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12264,7 +13134,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. La lumière est claire. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le portail de bois brille encore. Le doudou reste au chaud. Le pain, lui, est pour plus tard. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12404,7 +13274,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. La lumière est claire. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le portail de bois brille encore.
+narrateur|Le doudou reste au chaud.
+narrateur|Le pain, lui, est pour plus tard.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12432,7 +13323,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué le voisin. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12572,7 +13463,18 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12600,7 +13502,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le portail de bois brille encore. La pomme attend près du lit, sur le carnet fermé. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12740,7 +13642,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le portail de bois brille encore.
+narrateur|La pomme attend près du lit, sur le carnet fermé.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12768,7 +13691,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué le voisin. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12908,7 +13831,18 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12936,7 +13870,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le portail de bois brille encore. Le livre retrouve la chambre, tout doux, après la haie. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13076,7 +14010,30 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis le voisin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le portail de bois brille encore.
+narrateur|Le livre retrouve la chambre, tout doux, après la haie.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13104,7 +14061,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué le voisin. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13244,7 +14201,18 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué le voisin.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13272,7 +14240,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la maîtresse. On entend un oiseau. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Le doudou reste sur le lit, tout calme. La porte de l'école sent le bois mouillé. Un grelot de vélo sonne, loin, une fois. La maîtresse tient un livre fermé. Bonjour, Aniss. Bonjour. Bravo. Tu demandes avec s'il te plaît. S'il te plaît. La maîtresse ouvre le livre. Les pages sentent le papier. Merci. Merci, Aniss. Tu as dit les trois mots. Tu as fait du bon travail. Le livre a une image d'oiseau. Oui. On reste ensemble. Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13412,7 +14380,25 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la maîtresse. On entend un oiseau. papa montre lentement. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|La porte de l'école sent le bois mouillé.
+narrateur|Un grelot de vélo sonne, loin, une fois.
+narrateur|La maîtresse tient un livre fermé.
+maitresse|Bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+maman|Tu demandes avec s'il te plaît.
+enfant-m|S'il te plaît.
+narrateur|La maîtresse ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maitresse|Merci, Aniss.
+papa|Tu as dit les trois mots.
+maman|Tu as fait du bon travail.
+enfant-m|Le livre a une image d'oiseau.
+papa|Oui.
+papa|On reste ensemble.
+narrateur|Le radiateur de l'entrée fait un petit tic.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13440,7 +14426,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>Le livre de la maîtresse reste sous son bras. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13604,7 +14590,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|Le livre de la maîtresse reste sous son bras.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13632,7 +14621,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le livre de la maîtresse reste sous son bras. Le pain sent le four, loin du tapis de la chambre. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13772,7 +14761,27 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. Les chaussures font toc. Jules dit s'il te plaît. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Le pain sent le four, loin du tapis de la chambre.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13800,7 +14809,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la maîtresse. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13940,7 +14949,18 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13968,7 +14988,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le livre de la maîtresse reste sous son bras. La pomme roule près du cartable, sous l'œil de la maîtresse. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14108,7 +15128,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|La pomme roule près du cartable, sous l'œil de la maîtresse.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14136,7 +15177,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la maîtresse. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14276,7 +15317,18 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14304,7 +15356,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>Le doudou reste sur le lit, tout calme. Le livre de la maîtresse reste sous son bras. Le livre de la chambre s'ouvre dans la classe, tout calme. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14444,7 +15496,30 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la maîtresse.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|Le livre de la maîtresse reste sous son bras.
+narrateur|Le livre de la chambre s'ouvre dans la classe, tout calme.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14472,7 +15547,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la maîtresse. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14612,7 +15687,18 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14640,7 +15726,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi la boulangère. Le sol est un peu froid. papa montre lentement. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>Le doudou reste sur le lit, tout calme. La porte de la boulangerie s'ouvre. Une petite cloche fait ding. L'air chaud sent le beurre et le four. On dit bonjour, Aniss. Bonjour. Bravo. Tu demandes, maintenant. S'il te plaît. La boulangère a de la farine sur le tablier. Le bois du comptoir est lisse, un peu blanc. Merci. Tu as dit merci. Tu as fait du bon travail. Ça sent le pain. Oui. On reste près du comptoir. Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14780,7 +15866,24 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi la boulangère. Le sol est un peu froid. papa montre lentement. Jules dit bonjour. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. maman n'est pas loin.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|La porte de la boulangerie s'ouvre.
+narrateur|Une petite cloche fait ding.
+narrateur|L'air chaud sent le beurre et le four.
+maman|On dit bonjour, Aniss.
+enfant-m|Bonjour.
+papa|Bravo.
+papa|Tu demandes, maintenant.
+enfant-m|S'il te plaît.
+narrateur|La boulangère a de la farine sur le tablier.
+narrateur|Le bois du comptoir est lisse, un peu blanc.
+enfant-m|Merci.
+maman|Tu as dit merci.
+maman|Tu as fait du bon travail.
+enfant-m|Ça sent le pain.
+papa|Oui.
+papa|On reste près du comptoir.
+narrateur|Une croûte dorée brille derrière la vitre.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14808,7 +15911,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>La petite cloche a encore fait ding. On peut prendre le pain, une pomme, ou un livre. Tu demandes avec s'il te plaît. Ensuite, merci.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14972,7 +16075,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un livre.</t>
+          <t>narrateur|La petite cloche a encore fait ding.
+maman|On peut prendre le pain, une pomme, ou un livre.
+papa|Tu demandes avec s'il te plaît.
+maman|Ensuite, merci.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15000,7 +16106,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le pain. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>Le doudou reste sur le lit, tout calme. La petite cloche a encore fait ding. Le pain tiède réchauffe les mains, loin de la couverture. Le pain est encore tiède, dans un sachet. Le papier fait un bruit doux, tout rêche. Le pain, papa. Tu demandes comment ? S'il te plaît. Papa pose le sachet dans les deux mains d'Aniss. Merci. Et le bonjour, tu l'as dit ? Bonjour. Bravo. Les trois mots. Tu tiens le sachet ? Oui. Il est chaud. Ça sent le beurre, tout près du nez. Tu as fait du bon travail. Croc. C'est bon.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15140,7 +16246,27 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le pain. On entend un oiseau. Jules dit merci. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le pain tiède réchauffe les mains, loin de la couverture.
+narrateur|Le pain est encore tiède, dans un sachet.
+narrateur|Le papier fait un bruit doux, tout rêche.
+enfant-m|Le pain, papa.
+papa|Tu demandes comment ?
+enfant-m|S'il te plaît.
+narrateur|Papa pose le sachet dans les deux mains d'Aniss.
+enfant-m|Merci.
+maman|Et le bonjour, tu l'as dit ?
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu tiens le sachet ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+narrateur|Ça sent le beurre, tout près du nez.
+maman|Tu as fait du bon travail.
+enfant-m|Croc.
+enfant-m|C'est bon.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15168,7 +16294,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la boulangère. Il a demandé le pain. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Le sachet reste tiède, contre son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15308,7 +16434,18 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé le pain.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Le sachet reste tiède, contre son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15336,7 +16473,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint une pomme. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>Le doudou reste sur le lit, tout calme. La petite cloche a encore fait ding. La pomme claque un peu, sur le bois fariné. Une pomme rouge attend dans le panier. Elle brille. Elle est froide. La pomme, maman. Tu dis s'il te plaît ? S'il te plaît. Maman pose la pomme dans sa petite main. Merci. Tu as dit bonjour, aussi ? Bonjour. Bravo, Aniss. Tu veux un bout ? Oui. S'il te plaît. La pomme croque. Un peu sucrée, un peu d'eau. Merci, maman. Tu as fait du bon travail. Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15476,7 +16613,28 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint une pomme. Le sol est un peu froid. Jules salue tout doux. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|La petite cloche a encore fait ding.
+narrateur|La pomme claque un peu, sur le bois fariné.
+narrateur|Une pomme rouge attend dans le panier.
+narrateur|Elle brille.
+narrateur|Elle est froide.
+enfant-m|La pomme, maman.
+maman|Tu dis s'il te plaît ?
+enfant-m|S'il te plaît.
+narrateur|Maman pose la pomme dans sa petite main.
+enfant-m|Merci.
+papa|Tu as dit bonjour, aussi ?
+enfant-m|Bonjour.
+papa|Bravo, Aniss.
+maman|Tu veux un bout ?
+enfant-m|Oui.
+enfant-m|S'il te plaît.
+narrateur|La pomme croque.
+narrateur|Un peu sucrée, un peu d'eau.
+enfant-m|Merci, maman.
+maman|Tu as fait du bon travail.
+narrateur|Un reflet rouge danse sur le bois.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15504,7 +16662,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la boulangère. Il a demandé une pomme. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. Un reflet rouge danse encore sur le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15644,7 +16802,18 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé une pomme.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|Un reflet rouge danse encore sur le bois.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15672,7 +16841,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint un livre. Ça sent le pain chaud. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>Le doudou reste sur le lit, tout calme. La petite cloche a encore fait ding. Le livre a gardé l'odeur de la chambre, sous la cloche. Un livre fermé attend, tout calme. La couverture est lisse, un peu froide. Le livre, papa. Comment tu demandes ? S'il te plaît. Papa ouvre le livre. Les pages sentent le papier. Merci. On dit bonjour à l'histoire, aussi. Bonjour. Bravo. Les trois mots. Tu vois l'image ? Oui. Un oiseau gris. La page tourne. Frr, tout doux. Tu as fait du bon travail. Encore une page, s'il te plaît. Oui. Merci, Aniss.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15812,7 +16981,30 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint un livre. Ça sent le pain chaud. Jules répète les trois mots. Jules dit bonjour. Il dit s'il te plaît. Il dit merci. papa dit merci. la chambre, puis la boulangère.</t>
+          <t>narrateur|Le doudou reste sur le lit, tout calme.
+narrateur|La petite cloche a encore fait ding.
+narrateur|Le livre a gardé l'odeur de la chambre, sous la cloche.
+narrateur|Un livre fermé attend, tout calme.
+narrateur|La couverture est lisse, un peu froide.
+enfant-m|Le livre, papa.
+papa|Comment tu demandes ?
+enfant-m|S'il te plaît.
+narrateur|Papa ouvre le livre.
+narrateur|Les pages sentent le papier.
+enfant-m|Merci.
+maman|On dit bonjour à l'histoire, aussi.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Les trois mots.
+papa|Tu vois l'image ?
+enfant-m|Oui.
+enfant-m|Un oiseau gris.
+narrateur|La page tourne.
+narrateur|Frr, tout doux.
+maman|Tu as fait du bon travail.
+enfant-m|Encore une page, s'il te plaît.
+papa|Oui.
+papa|Merci, Aniss.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15840,7 +17032,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a dit les mots dans la chambre. Il a salué la boulangère. Il a demandé un livre. Bonjour. S'il te plaît. Merci. Bravo, Aniss. Tu as fait du bon travail. Tu as dit les trois mots ? Oui, papa. La page reste ouverte, sur l'oiseau gris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15980,7 +17172,18 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a dit les mots dans la chambre.
+narrateur|Il a salué la boulangère.
+narrateur|Il a demandé un livre.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+papa|Tu as dit les trois mots ?
+enfant-m|Oui, papa.
+narrateur|La page reste ouverte, sur l'oiseau gris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16002,7 +17205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16040,6 +17243,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-005.xlsx
+++ b/stories/arbres/TREE-COL-005.xlsx
@@ -7092,7 +7092,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît | s'il te plait | sil te plait | please</t>
+          <t>s'il te plaît | s'il te plait | sil te plait</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15006,17 +15006,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.</t>
+          <t>Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Toute la phrase, oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Toute la phrase, oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le pain de la phrase entière chauffe le tissu. L'auvent n'a pas touché la croûte. Elle a eu toute la phrase. Toute la phrase, oui. Merci, le col était ouvert. Le manteau s'ouvre, une bouffée d'air de soupe. Le livre sous le bras est resté à l'école. Un tic de gouttière, puis le silence du pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15157,7 +15157,7 @@
           <t>narrateur|Le pain de la phrase entière chauffe le tissu.
 narrateur|L'auvent n'a pas touché la croûte.
 enfant-m|Elle a eu toute la phrase.
-maitresse|Oui.
+maman|Toute la phrase, oui.
 papa|Merci, le col était ouvert.
 narrateur|Le manteau s'ouvre, une bouffée d'air de soupe.
 narrateur|Le livre sous le bras est resté à l'école.
@@ -17447,7 +17447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17504,6 +17504,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
